--- a/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_215_R22.xlsx
+++ b/informes_data/Euroleague/2025-26/Regular_Season/individual/NP_play_by_play_EL_215_R22.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>3.5081</v>
+        <v>2.5862</v>
       </c>
       <c r="E2" t="n">
-        <v>3.8823</v>
+        <v>2.9269</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.3743</v>
+        <v>-0.3407</v>
       </c>
       <c r="G2" t="n">
         <v>3.6135</v>
@@ -610,13 +610,13 @@
         <v>2.0876</v>
       </c>
       <c r="S2" t="n">
-        <v>0.6084000000000001</v>
+        <v>-0.3134</v>
       </c>
       <c r="T2" t="n">
-        <v>1.0974</v>
+        <v>0.1419</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.4889</v>
+        <v>-0.4553</v>
       </c>
       <c r="V2" t="n">
         <v>0.6778999999999999</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9825</v>
+        <v>1.6118</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.4906</v>
+        <v>0.4412</v>
       </c>
       <c r="F3" t="n">
-        <v>1.4731</v>
+        <v>1.1706</v>
       </c>
       <c r="G3" t="n">
         <v>-0.0421</v>
@@ -688,13 +688,13 @@
         <v>2.3195</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.1532</v>
+        <v>-0.5239</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.5604</v>
+        <v>-0.6286</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4072</v>
+        <v>0.1048</v>
       </c>
       <c r="V3" t="n">
         <v>-0.1418</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. BACON</t>
+          <t>A. ABASS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.5786</v>
+        <v>-0.2917</v>
       </c>
       <c r="E4" t="n">
-        <v>-1.2639</v>
+        <v>0.7498</v>
       </c>
       <c r="F4" t="n">
-        <v>1.8424</v>
+        <v>-1.0415</v>
       </c>
       <c r="G4" t="n">
-        <v>-2.5432</v>
+        <v>0.7098</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.6869</v>
+        <v>-0.4848</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1437</v>
+        <v>1.1946</v>
       </c>
       <c r="J4" t="n">
-        <v>-1.2633</v>
+        <v>1.3354</v>
       </c>
       <c r="K4" t="n">
-        <v>-2.0426</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7793</v>
+        <v>1.2514</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.2799</v>
+        <v>-0.6256</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.6443</v>
+        <v>-0.5688</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.6356000000000001</v>
+        <v>-0.0568</v>
       </c>
       <c r="P4" t="n">
-        <v>0.6959</v>
+        <v>0.9278</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.8556</v>
+        <v>0.9278</v>
       </c>
       <c r="S4" t="n">
-        <v>1.6373</v>
+        <v>-0.8571</v>
       </c>
       <c r="T4" t="n">
-        <v>0.08699999999999999</v>
+        <v>-0.5856</v>
       </c>
       <c r="U4" t="n">
-        <v>1.5503</v>
+        <v>-0.2715</v>
       </c>
       <c r="V4" t="n">
-        <v>0.7886</v>
+        <v>-1.0722</v>
       </c>
       <c r="W4" t="n">
-        <v>1.0722</v>
+        <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.2836</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. KABENGELE</t>
+          <t>D. BACON</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.1352</v>
+        <v>-0.584</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.1831</v>
+        <v>-1.5863</v>
       </c>
       <c r="F5" t="n">
-        <v>0.0478</v>
+        <v>1.0023</v>
       </c>
       <c r="G5" t="n">
-        <v>-0.9067</v>
+        <v>-2.5432</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.9976</v>
+        <v>-2.6869</v>
       </c>
       <c r="I5" t="n">
-        <v>1.0908</v>
+        <v>0.1437</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.7849</v>
+        <v>-1.2633</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.2499</v>
+        <v>-2.0426</v>
       </c>
       <c r="L5" t="n">
-        <v>0.465</v>
+        <v>0.7793</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.1219</v>
+        <v>-1.2799</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.7477</v>
+        <v>-0.6443</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6258</v>
+        <v>-0.6356000000000001</v>
       </c>
       <c r="P5" t="n">
-        <v>0.4639</v>
+        <v>0.6959</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4639</v>
+        <v>1.8556</v>
       </c>
       <c r="S5" t="n">
-        <v>0.4494</v>
+        <v>0.4747</v>
       </c>
       <c r="T5" t="n">
-        <v>0.6018</v>
+        <v>-0.2355</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.1524</v>
+        <v>0.7101</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1418</v>
+        <v>0.7886</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>1.0722</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1418</v>
+        <v>-0.2836</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A. ABASS</t>
+          <t>M. KABENGELE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.9458</v>
+        <v>-0.7704</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3645</v>
+        <v>-0.7847</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3103</v>
+        <v>0.0142</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7098</v>
+        <v>-0.9067</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.4848</v>
+        <v>-1.9976</v>
       </c>
       <c r="I6" t="n">
-        <v>1.1946</v>
+        <v>1.0908</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3354</v>
+        <v>-0.7849</v>
       </c>
       <c r="K6" t="n">
-        <v>0.08400000000000001</v>
+        <v>-1.2499</v>
       </c>
       <c r="L6" t="n">
-        <v>1.2514</v>
+        <v>0.465</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6256</v>
+        <v>-0.1219</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5688</v>
+        <v>-0.7477</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.0568</v>
+        <v>0.6258</v>
       </c>
       <c r="P6" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="Q6" t="n">
         <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>0.9278</v>
+        <v>0.4639</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5112</v>
+        <v>-0.1858</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.9709</v>
+        <v>0.0002</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.5403</v>
+        <v>-0.186</v>
       </c>
       <c r="V6" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-1.0722</v>
+        <v>-0.1418</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>K. KAMENJAS</t>
+          <t>D. BERTANS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,64 +955,64 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.044</v>
+        <v>-1.1606</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5905</v>
+        <v>-1.4361</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.4535</v>
+        <v>0.2755</v>
       </c>
       <c r="G7" t="n">
-        <v>-1.0793</v>
+        <v>-1.1215</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.1224</v>
+        <v>-0.228</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9569</v>
+        <v>-0.8935</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.8541</v>
+        <v>-0.8104</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.215</v>
+        <v>-0.131</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.6391</v>
+        <v>-0.6794</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.2252</v>
+        <v>-0.3111</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0926</v>
+        <v>-0.097</v>
       </c>
       <c r="O7" t="n">
-        <v>-0.3178</v>
+        <v>-0.214</v>
       </c>
       <c r="P7" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="Q7" t="n">
         <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3917</v>
+        <v>1.6237</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.2842</v>
+        <v>-0.338</v>
       </c>
       <c r="T7" t="n">
-        <v>0.2636</v>
+        <v>-0.3732</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.5478</v>
+        <v>0.0351</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.0722</v>
+        <v>-1.3247</v>
       </c>
       <c r="W7" t="n">
-        <v>0</v>
+        <v>-0.2525</v>
       </c>
       <c r="X7" t="n">
         <v>-1.0722</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>K. PREPELIC</t>
+          <t>K. KAMENJAS</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.947</v>
+        <v>-1.3643</v>
       </c>
       <c r="E8" t="n">
-        <v>-2.0138</v>
+        <v>-0.9444</v>
       </c>
       <c r="F8" t="n">
-        <v>0.0668</v>
+        <v>-0.4199</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5557</v>
+        <v>-1.0793</v>
       </c>
       <c r="H8" t="n">
-        <v>0.2473</v>
+        <v>-0.1224</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.8031</v>
+        <v>-0.9569</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.4807</v>
+        <v>-0.8541</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2689</v>
+        <v>-0.215</v>
       </c>
       <c r="L8" t="n">
-        <v>-0.7495000000000001</v>
+        <v>-0.6391</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.0751</v>
+        <v>-0.2252</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.0216</v>
+        <v>0.0926</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.0535</v>
+        <v>-0.3178</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.9278</v>
+        <v>1.3917</v>
       </c>
       <c r="Q8" t="n">
-        <v>-1.1598</v>
+        <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.232</v>
+        <v>1.3917</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.4635</v>
+        <v>-0.6045</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3734</v>
+        <v>-0.09030000000000001</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.0901</v>
+        <v>-0.5142</v>
       </c>
       <c r="V8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>0</v>
+        <v>-1.0722</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>D. BERTANS</t>
+          <t>K. PREPELIC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.1686</v>
+        <v>-1.7715</v>
       </c>
       <c r="E9" t="n">
-        <v>-2.1752</v>
+        <v>-1.9391</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0067</v>
+        <v>0.1676</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.1215</v>
+        <v>-0.5557</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.228</v>
+        <v>0.2473</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.8935</v>
+        <v>-0.8031</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.8104</v>
+        <v>-0.4807</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.131</v>
+        <v>0.2689</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6794</v>
+        <v>-0.7495000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3111</v>
+        <v>-0.0751</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.097</v>
+        <v>-0.0216</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.214</v>
+        <v>-0.0535</v>
       </c>
       <c r="P9" t="n">
-        <v>1.6237</v>
+        <v>-0.9278</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-1.1598</v>
       </c>
       <c r="R9" t="n">
-        <v>1.6237</v>
+        <v>0.232</v>
       </c>
       <c r="S9" t="n">
-        <v>-1.346</v>
+        <v>-0.288</v>
       </c>
       <c r="T9" t="n">
-        <v>-1.1123</v>
+        <v>-0.2987</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.2337</v>
+        <v>0.0108</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.3247</v>
+        <v>0</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.2525</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0722</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.4253</v>
+        <v>-2.6025</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.3308</v>
+        <v>-2.7096</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.0945</v>
+        <v>0.1072</v>
       </c>
       <c r="G10" t="n">
         <v>-1.3951</v>
@@ -1234,13 +1234,13 @@
         <v>0.9278</v>
       </c>
       <c r="S10" t="n">
-        <v>-1.4813</v>
+        <v>-0.6585</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.1123</v>
+        <v>-0.4911</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.369</v>
+        <v>-0.1674</v>
       </c>
       <c r="V10" t="n">
         <v>2.0026</v>
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.9554</v>
+        <v>-2.7115</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.8687</v>
+        <v>-2.8937</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0867</v>
+        <v>0.1822</v>
       </c>
       <c r="G11" t="n">
         <v>-0.186</v>
@@ -1312,13 +1312,13 @@
         <v>0.9278</v>
       </c>
       <c r="S11" t="n">
-        <v>-1.8415</v>
+        <v>-0.5977</v>
       </c>
       <c r="T11" t="n">
-        <v>-1.0455</v>
+        <v>-0.07049999999999999</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.796</v>
+        <v>-0.5272</v>
       </c>
       <c r="V11" t="n">
         <v>-0.5361</v>
@@ -1345,10 +1345,10 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-8.552099999999999</v>
+        <v>-7.058500000000001</v>
       </c>
       <c r="E12" t="n">
-        <v>-9.6698</v>
+        <v>-8.176000000000002</v>
       </c>
       <c r="F12" t="n">
         <v>1.1175</v>
@@ -1360,7 +1360,7 @@
         <v>-5.8818</v>
       </c>
       <c r="I12" t="n">
-        <v>2.3753</v>
+        <v>2.375299999999999</v>
       </c>
       <c r="J12" t="n">
         <v>1.338799999999999</v>
@@ -1369,7 +1369,7 @@
         <v>-1.6046</v>
       </c>
       <c r="L12" t="n">
-        <v>2.9433</v>
+        <v>2.943300000000001</v>
       </c>
       <c r="M12" t="n">
         <v>-4.8453</v>
@@ -1390,13 +1390,13 @@
         <v>12.7574</v>
       </c>
       <c r="S12" t="n">
-        <v>-5.3858</v>
+        <v>-3.8922</v>
       </c>
       <c r="T12" t="n">
-        <v>-4.125</v>
+        <v>-2.6314</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.2607</v>
+        <v>-1.2608</v>
       </c>
       <c r="V12" t="n">
         <v>-0.8196999999999999</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.8147</v>
+        <v>6.9978</v>
       </c>
       <c r="E13" t="n">
-        <v>6.7418</v>
+        <v>3.675</v>
       </c>
       <c r="F13" t="n">
-        <v>4.0729</v>
+        <v>3.3228</v>
       </c>
       <c r="G13" t="n">
         <v>1.9717</v>
@@ -1468,13 +1468,13 @@
         <v>1.8556</v>
       </c>
       <c r="S13" t="n">
-        <v>6.4871</v>
+        <v>2.6703</v>
       </c>
       <c r="T13" t="n">
-        <v>4.3095</v>
+        <v>1.2428</v>
       </c>
       <c r="U13" t="n">
-        <v>2.1776</v>
+        <v>1.4275</v>
       </c>
       <c r="V13" t="n">
         <v>1.8919</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>1.7247</v>
+        <v>1.849</v>
       </c>
       <c r="E14" t="n">
-        <v>0.9882</v>
+        <v>1.2241</v>
       </c>
       <c r="F14" t="n">
-        <v>0.7365</v>
+        <v>0.6249</v>
       </c>
       <c r="G14" t="n">
         <v>0.4179</v>
@@ -1546,13 +1546,13 @@
         <v>1.1598</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2372</v>
+        <v>0.3615</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5975</v>
+        <v>-0.3615</v>
       </c>
       <c r="U14" t="n">
-        <v>0.8347</v>
+        <v>0.7231</v>
       </c>
       <c r="V14" t="n">
         <v>0.1418</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.2434</v>
+        <v>1.8211</v>
       </c>
       <c r="E15" t="n">
-        <v>0.9471000000000001</v>
+        <v>1.065</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2963</v>
+        <v>0.756</v>
       </c>
       <c r="G15" t="n">
         <v>2.8736</v>
@@ -1624,13 +1624,13 @@
         <v>0.6959</v>
       </c>
       <c r="S15" t="n">
-        <v>0.2254</v>
+        <v>0.803</v>
       </c>
       <c r="T15" t="n">
-        <v>0.5034</v>
+        <v>0.6214</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.2781</v>
+        <v>0.1817</v>
       </c>
       <c r="V15" t="n">
         <v>0</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.1177</v>
+        <v>1.776</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.7793</v>
+        <v>-0.7177</v>
       </c>
       <c r="F16" t="n">
-        <v>2.897</v>
+        <v>2.4938</v>
       </c>
       <c r="G16" t="n">
         <v>-0.8028999999999999</v>
@@ -1702,13 +1702,13 @@
         <v>1.8556</v>
       </c>
       <c r="S16" t="n">
-        <v>0.065</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="T16" t="n">
-        <v>-1.0297</v>
+        <v>0.0318</v>
       </c>
       <c r="U16" t="n">
-        <v>1.0947</v>
+        <v>0.6915</v>
       </c>
       <c r="V16" t="n">
         <v>0</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. DIOUF</t>
+          <t>C. EDWARDS</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.0945</v>
+        <v>0.5064</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2642</v>
+        <v>-1.243</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.1697</v>
+        <v>1.7494</v>
       </c>
       <c r="G17" t="n">
-        <v>1.2041</v>
+        <v>0.1923</v>
       </c>
       <c r="H17" t="n">
-        <v>1.9903</v>
+        <v>1.8387</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.7862</v>
+        <v>-1.6464</v>
       </c>
       <c r="J17" t="n">
-        <v>1.6936</v>
+        <v>0.2564</v>
       </c>
       <c r="K17" t="n">
-        <v>1.5832</v>
+        <v>1.1602</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1104</v>
+        <v>-0.9038</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4895</v>
+        <v>-0.0641</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4071</v>
+        <v>0.6785</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.8966</v>
+        <v>-0.7426</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.8556</v>
+        <v>-0.6959</v>
       </c>
       <c r="Q17" t="n">
         <v>-2.3195</v>
       </c>
       <c r="R17" t="n">
-        <v>0.4639</v>
+        <v>1.6237</v>
       </c>
       <c r="S17" t="n">
-        <v>0.21</v>
+        <v>0.7264</v>
       </c>
       <c r="T17" t="n">
-        <v>0.3541</v>
+        <v>0.0004</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1441</v>
+        <v>0.726</v>
       </c>
       <c r="V17" t="n">
-        <v>0.5361</v>
+        <v>0.2836</v>
       </c>
       <c r="W17" t="n">
-        <v>0.5361</v>
+        <v>0.8197</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.5361</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>N. AKELE</t>
+          <t>M. DIOUF</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,64 +1813,64 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1337</v>
+        <v>0.319</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5117</v>
+        <v>0.2642</v>
       </c>
       <c r="F18" t="n">
-        <v>0.378</v>
+        <v>0.0548</v>
       </c>
       <c r="G18" t="n">
-        <v>0.3219</v>
+        <v>1.2041</v>
       </c>
       <c r="H18" t="n">
-        <v>0.305</v>
+        <v>1.9903</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0168</v>
+        <v>-0.7862</v>
       </c>
       <c r="J18" t="n">
-        <v>0.4433</v>
+        <v>1.6936</v>
       </c>
       <c r="K18" t="n">
-        <v>0.3697</v>
+        <v>1.5832</v>
       </c>
       <c r="L18" t="n">
-        <v>0.0736</v>
+        <v>0.1104</v>
       </c>
       <c r="M18" t="n">
-        <v>-0.1215</v>
+        <v>-0.4895</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.06469999999999999</v>
+        <v>0.4071</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.0568</v>
+        <v>-0.8966</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4639</v>
+        <v>-1.8556</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1598</v>
+        <v>-2.3195</v>
       </c>
       <c r="R18" t="n">
-        <v>0.6959</v>
+        <v>0.4639</v>
       </c>
       <c r="S18" t="n">
-        <v>0.0083</v>
+        <v>0.4345</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2047</v>
+        <v>0.3541</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.1964</v>
+        <v>0.0804</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.5361</v>
       </c>
       <c r="X18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>C. EDWARDS</t>
+          <t>N. AKELE</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,67 +1891,67 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.1772</v>
+        <v>-0.2688</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.4225</v>
+        <v>-0.7476</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2453</v>
+        <v>0.4788</v>
       </c>
       <c r="G19" t="n">
-        <v>0.1923</v>
+        <v>0.3219</v>
       </c>
       <c r="H19" t="n">
-        <v>1.8387</v>
+        <v>0.305</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.6464</v>
+        <v>0.0168</v>
       </c>
       <c r="J19" t="n">
-        <v>0.2564</v>
+        <v>0.4433</v>
       </c>
       <c r="K19" t="n">
-        <v>1.1602</v>
+        <v>0.3697</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.9038</v>
+        <v>0.0736</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0641</v>
+        <v>-0.1215</v>
       </c>
       <c r="N19" t="n">
-        <v>0.6785</v>
+        <v>-0.06469999999999999</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7426</v>
+        <v>-0.0568</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6959</v>
+        <v>-0.4639</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.3195</v>
+        <v>-1.1598</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6237</v>
+        <v>0.6959</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9572000000000001</v>
+        <v>-0.1267</v>
       </c>
       <c r="T19" t="n">
-        <v>-1.1791</v>
+        <v>-0.0312</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2219</v>
+        <v>-0.0955</v>
       </c>
       <c r="V19" t="n">
-        <v>0.2836</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>0.8197</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5361</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20">
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.8754</v>
+        <v>-1.59</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.1359</v>
+        <v>-0.2538</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.7395</v>
+        <v>-1.3362</v>
       </c>
       <c r="G20" t="n">
         <v>0.4015</v>
@@ -2014,13 +2014,13 @@
         <v>1.3917</v>
       </c>
       <c r="S20" t="n">
-        <v>0.1511</v>
+        <v>0.4364</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0395</v>
+        <v>-0.0784</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1116</v>
+        <v>0.5149</v>
       </c>
       <c r="V20" t="n">
         <v>-2.428</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-3.2567</v>
+        <v>-2.0721</v>
       </c>
       <c r="E21" t="n">
-        <v>-5.2095</v>
+        <v>-4.3839</v>
       </c>
       <c r="F21" t="n">
-        <v>1.9529</v>
+        <v>2.3118</v>
       </c>
       <c r="G21" t="n">
         <v>-3.0737</v>
@@ -2092,13 +2092,13 @@
         <v>1.8556</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.0411</v>
+        <v>0.1434</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3443</v>
+        <v>-0.5185999999999999</v>
       </c>
       <c r="U21" t="n">
-        <v>0.3031</v>
+        <v>0.662</v>
       </c>
       <c r="V21" t="n">
         <v>0.3943</v>
@@ -2125,25 +2125,25 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>8.552000000000001</v>
+        <v>9.3384</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.117600000000001</v>
+        <v>-1.1177</v>
       </c>
       <c r="F22" t="n">
-        <v>9.669700000000001</v>
+        <v>10.4561</v>
       </c>
       <c r="G22" t="n">
         <v>3.5064</v>
       </c>
       <c r="H22" t="n">
-        <v>5.8817</v>
+        <v>5.881699999999999</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.375300000000001</v>
+        <v>-2.3753</v>
       </c>
       <c r="J22" t="n">
-        <v>4.845199999999998</v>
+        <v>4.8452</v>
       </c>
       <c r="K22" t="n">
         <v>4.2775</v>
@@ -2170,16 +2170,16 @@
         <v>11.5977</v>
       </c>
       <c r="S22" t="n">
-        <v>5.3858</v>
+        <v>6.172099999999999</v>
       </c>
       <c r="T22" t="n">
-        <v>1.2606</v>
+        <v>1.2608</v>
       </c>
       <c r="U22" t="n">
-        <v>4.125</v>
+        <v>4.911599999999999</v>
       </c>
       <c r="V22" t="n">
-        <v>0.8197</v>
+        <v>0.8197000000000002</v>
       </c>
       <c r="W22" t="n">
         <v>5.533900000000001</v>
